--- a/docs/CAS_Duplicate_Merge_Checklist_2026-05-07.xlsx
+++ b/docs/CAS_Duplicate_Merge_Checklist_2026-05-07.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -407,7 +407,7 @@
     <col min="5" max="5" width="60.83203125" customWidth="1"/>
     <col min="6" max="6" width="24.83203125" customWidth="1"/>
     <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="8" max="8" width="60.83203125" customWidth="1"/>
     <col min="9" max="9" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -434,7 +434,7 @@
         <v>DELETE — Click to open</v>
       </c>
       <c r="H1" t="str">
-        <v>Action</v>
+        <v>Note</v>
       </c>
       <c r="I1" t="str">
         <v>Status (Jan to fill)</v>
@@ -463,7 +463,7 @@
         <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002296017</v>
       </c>
       <c r="H2" t="str">
-        <v>Open BOTH, verify identical, then DELETE the right-hand one</v>
+        <v>Original was synced via background worker; dup from re-submit</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -492,7 +492,7 @@
         <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002297006</v>
       </c>
       <c r="H3" t="str">
-        <v>Open BOTH, verify identical, then DELETE the right-hand one</v>
+        <v>Original was synced via background worker; dup from re-submit</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002298013</v>
       </c>
       <c r="H4" t="str">
-        <v>Open BOTH, verify identical, then DELETE the right-hand one</v>
+        <v>Original was synced via background worker; dup from re-submit</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -550,7 +550,7 @@
         <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002303017</v>
       </c>
       <c r="H5" t="str">
-        <v>Open BOTH, verify identical, then DELETE the right-hand one</v>
+        <v>Original was synced via background worker; dup from re-submit</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -579,7 +579,7 @@
         <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002297008</v>
       </c>
       <c r="H6" t="str">
-        <v>Open BOTH, verify identical, then DELETE the right-hand one</v>
+        <v>Original was synced via background worker; dup from re-submit</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -608,7 +608,7 @@
         <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002307023</v>
       </c>
       <c r="H7" t="str">
-        <v>Open BOTH, verify identical, then DELETE the right-hand one</v>
+        <v>Original was synced via background worker; dup from re-submit</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -637,7 +637,7 @@
         <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002305021</v>
       </c>
       <c r="H8" t="str">
-        <v>Open BOTH, verify identical, then DELETE the right-hand one</v>
+        <v>Original was synced via background worker; dup from re-submit</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -666,7 +666,7 @@
         <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002305023</v>
       </c>
       <c r="H9" t="str">
-        <v>Open BOTH, verify identical, then DELETE the right-hand one</v>
+        <v>Original was synced via background worker; dup from re-submit</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -695,7 +695,7 @@
         <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002298015</v>
       </c>
       <c r="H10" t="str">
-        <v>Open BOTH, verify identical, then DELETE the right-hand one</v>
+        <v>Original was synced via background worker; dup from re-submit</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -724,22 +724,80 @@
         <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002307021</v>
       </c>
       <c r="H11" t="str">
-        <v>Open BOTH, verify identical, then DELETE the right-hand one</v>
+        <v>Original was synced via background worker; dup from re-submit</v>
       </c>
       <c r="I11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Emilie Theberge</v>
+      </c>
+      <c r="C12" t="str">
+        <v>emilie.theberge@ubc.ca</v>
+      </c>
+      <c r="D12" t="str">
+        <v>6999043000002288015</v>
+      </c>
+      <c r="E12" t="str">
+        <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002288015</v>
+      </c>
+      <c r="F12" t="str">
+        <v>6999043000002305026</v>
+      </c>
+      <c r="G12" t="str">
+        <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002305026</v>
+      </c>
+      <c r="H12" t="str">
+        <v>BOTH from May 8 rescue (script ran twice)</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Niloufar Ahmadbeigi</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ahmadbeigi@hhsc.ca</v>
+      </c>
+      <c r="D13" t="str">
+        <v>6999043000002288014</v>
+      </c>
+      <c r="E13" t="str">
+        <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002288014</v>
+      </c>
+      <c r="F13" t="str">
+        <v>6999043000002291032</v>
+      </c>
+      <c r="G13" t="str">
+        <v>https://crm.zoho.com/crm/org/tab/Leads/6999043000002291032</v>
+      </c>
+      <c r="H13" t="str">
+        <v>BOTH from May 8 rescue (script ran twice)</v>
+      </c>
+      <c r="I13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="120.83203125" customWidth="1"/>
@@ -774,7 +832,7 @@
         <v>2a</v>
       </c>
       <c r="B4" t="str">
-        <v>Click the "KEEP — Click to open" link. Verify the record looks correct (this is the OLDER one, created via background worker).</v>
+        <v>Click the "KEEP — Click to open" link to verify the older record.</v>
       </c>
     </row>
     <row r="5">
@@ -782,7 +840,7 @@
         <v>2b</v>
       </c>
       <c r="B5" t="str">
-        <v>Click the "DELETE — Click to open" link. Verify it has identical name + email (it is the duplicate from re-submit).</v>
+        <v>Click the "DELETE — Click to open" link to verify it has the same name + email.</v>
       </c>
     </row>
     <row r="6">
@@ -790,7 +848,7 @@
         <v>2c</v>
       </c>
       <c r="B6" t="str">
-        <v>Optional: in Zoho, use Settings → Data Administration → Find Duplicates by Email if you prefer the bulk merge UI.</v>
+        <v>Optional: Use Zoho Settings → Data Administration → Find Duplicates by Email for bulk handling.</v>
       </c>
     </row>
     <row r="7">
@@ -798,7 +856,7 @@
         <v>2d</v>
       </c>
       <c r="B7" t="str">
-        <v>Delete the duplicate record (or use Zoho Merge to combine, keeping the older).</v>
+        <v>Delete the duplicate (or use Zoho Merge to combine, keeping the older).</v>
       </c>
     </row>
     <row r="8">
@@ -806,7 +864,7 @@
         <v>2e</v>
       </c>
       <c r="B8" t="str">
-        <v>Mark the row Status as "DONE" so you can track progress.</v>
+        <v>Mark Status as "DONE" so you can track progress.</v>
       </c>
     </row>
     <row r="9">
@@ -814,7 +872,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="str">
-        <v>After all 10 pairs are merged, total Lead count should drop from 298 → 288.</v>
+        <v>After all 12 pairs are merged, total Lead count should drop from 303 → 291.</v>
       </c>
     </row>
     <row r="10">
@@ -822,12 +880,20 @@
         <v>4</v>
       </c>
       <c r="B10" t="str">
-        <v>Note: Mary O'Sullivan also has a 3rd record (#264 sub) that was already manually pushed in a prior session — check for that too.</v>
+        <v>Note: Mary O'Sullivan also has a 3rd record (#264 sub) manually pushed in a prior session — also check for that.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Note: Emilie + Niloufar were both pushed twice during the May 8 rescue (the script was rerun before the first result was visible). Both copies are in CRM and need merging.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>